--- a/output/2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx
@@ -464,7 +464,6 @@
           <t>Ex-OPREMA d.o.o.</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Zagreb</t>
@@ -480,7 +479,6 @@
           <t>01 5616110</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore STAHL (apparecchiature antideflagranti); produzione/manutenzione dispositivi Ex; copertura nazionale, include Varazdinska</t>
@@ -639,7 +637,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>b2b@tipteh.com</t>
@@ -689,7 +686,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agente/distributore e centro assistenza autorizzato Nilfisk, inclusi aspiratori industriali ATEX (es. CFM 3907/18 Z21 ATEX); copertura nazionale, include Varazdinska</t>
+          <t>Agente/distributore e centro assistenza autorizzato Nilfisk, inclusi aspiratori industriali ATEX (es. CFM 3907/18 Z21 ATEX); copertura nazionale, include Varazdinska [DUPLICATO — vedi anche: 2026-09-07_19_Croazia_Zagrebacka_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -761,7 +758,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>informa-ka@informa-ka.hr</t>
@@ -804,10 +800,9 @@
           <t>+385 1 6553 655</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Distributore ventilatori ATEX (conformi direttiva 2014/34/EU e norma EN 14986) e attrezzature antincendio; copertura nazionale, include Varazdinska</t>
+          <t>Distributore ventilatori ATEX (conformi direttiva 2014/34/EU e norma EN 14986) e attrezzature antincendio; copertura nazionale, include Varazdinska [DUPLICATO — vedi anche: 2026-09-07_22_Croazia_Zagrebacka_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -884,7 +879,6 @@
           <t>+385 1 5578565</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Ente di certificazione IECEx e Organismo Notificato UE n.2829 per apparecchiature Ex secondo ATEX 2014/34/EU; servizio di certificazione/consulenza; copertura nazionale, include Varazdinska</t>
@@ -917,8 +911,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Distributore paranchi/dizalice ATEX (pneumatici serie ENDO-ATC e a catena manuale) per zone Ex 1-2 e 21-22; copertura nazionale, include Varazdinska</t>
@@ -963,7 +955,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Distributore paranchi elettrici e pneumatici ATEX (serie ENDO, elettrocatena sincronizzata); copertura nazionale, include Varazdinska</t>
+          <t>Distributore paranchi elettrici e pneumatici ATEX (serie ENDO, elettrocatena sincronizzata); copertura nazionale, include Varazdinska [DUPLICATO — vedi anche: 2026-09-07_22_Croazia_Zagrebacka_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">

--- a/output/2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-13_02_Croazia_Varazdinska_ATEX_Equipment-Services.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -570,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
